--- a/data/google_news_dedup_30_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_30_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -535,32 +535,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>China's off-price sales boom - news.cgtn.com</t>
+          <t>Amazon CEO Andy Jassy Explains How Soaring Chip Prices, Supply Crunch Could Pressure AMZN's CapEx: 'We Ha - Benzinga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>China's off-price sales boom - news.cgtn.com</t>
+          <t>Amazon CEO Andy Jassy Explains How Soaring Chip Prices, Supply Crunch Could Pressure AMZN's CapEx: 'We Ha - Benzinga</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 06:56:50 GMT</t>
+          <t>Thu, 30 Apr 2026 08:21:29 GMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxObVJDTklXX0kzRWZGOGE3RlVodVFSQmRZb0RhQ0gwWEN6WnJoT3gyaV81SHVmMzU2NExXTDZCQi1GZVNOU2Y3UFNMSnFkalpRTm5PUjFlSjdNT3hFNnBqNHFENjhUVkV1THI1Z3E5cWVaLTNZYnJicFJ3WW9sbmlaWk5hWXk3ZDltVVhXbG5xcVc3Mkx2Y3RZZg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOUXVNcFZRZFRFWDNxdndFMEJkbm1lVGFRdkJpSFNfRHRtMVNDTk5GLXFSdnlCREp0Y3NSOVlwVlBBRGV3Ylp2WEM2VENwZm4xdHFqdHFkaFNHUUNxTTJZeS1xQ3BBZmg4VGE1TU81Wl9FeG84ZHdsT3pjZ0NBYUd1NzdwUDVXajFYOUlZcUVqWXBBQjZXc2E2SjdQc3hkOHN4YWlaWk94Z09SUmp6Y1NNT2VmSmE0ejJzd1V2MzJPWXBnYXp1LVQtcl9zdjBsU2YyZDFHRmsyQ1BMempJcVhaRjJERzZCQl8zUDJPZHFZb00yb0VSX2ViYzZOaTlfVnJtaUE?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46142.28946759259</v>
+        <v>46142.34825231481</v>
       </c>
     </row>
     <row r="4">
@@ -600,22 +600,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amazon CEO Andy Jassy Explains How Soaring Chip Prices, Supply Crunch Could Pressure AMZN's CapEx: 'We Ha - Benzinga</t>
+          <t>Amazon.com announces first quarter results - About Amazon</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Amazon CEO Andy Jassy Explains How Soaring Chip Prices, Supply Crunch Could Pressure AMZN's CapEx: 'We Ha - Benzinga</t>
+          <t>Amazon.com announces first quarter results - About Amazon</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 08:21:29 GMT</t>
+          <t>Thu, 30 Apr 2026 08:32:27 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggJBVV95cUxOUXVNcFZRZFRFWDNxdndFMEJkbm1lVGFRdkJpSFNfRHRtMVNDTk5GLXFSdnlCREp0Y3NSOVlwVlBBRGV3Ylp2WEM2VENwZm4xdHFqdHFkaFNHUUNxTTJZeS1xQ3BBZmg4VGE1TU81Wl9FeG84ZHdsT3pjZ0NBYUd1NzdwUDVXajFYOUlZcUVqWXBBQjZXc2E2SjdQc3hkOHN4YWlaWk94Z09SUmp6Y1NNT2VmSmE0ejJzd1V2MzJPWXBnYXp1LVQtcl9zdjBsU2YyZDFHRmsyQ1BMempJcVhaRjJERzZCQl8zUDJPZHFZb00yb0VSX2ViYzZOaTlfVnJtaUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNcmlXNUY0YkNobmFkeEhiaEVvRDJfZXhCUTNIUnF3YUN5c011VlhPdngxdWZmcWRMM3hfWnlibXdvYWRmYl95WkdSaUw3aFRZUDdFR0FkRjNuQ24zazAxSENzUEtCRGh5TXJ1bW9taG1Mb2ZQdWhucTVZc3VyR3hrNTRn?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46142.34825231481</v>
+        <v>46142.35586805556</v>
       </c>
     </row>
     <row r="5">
@@ -655,22 +655,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Amazon.com announces first quarter results - About Amazon</t>
+          <t>Dubai Chamber of Commerce and FedEx discuss supply chain readiness with representatives from 196 companies - ZAWYA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Amazon.com announces first quarter results - About Amazon</t>
+          <t>Dubai Chamber of Commerce and FedEx discuss supply chain readiness with representatives from 196 companies - ZAWYA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 08:32:27 GMT</t>
+          <t>Thu, 30 Apr 2026 09:09:36 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNcmlXNUY0YkNobmFkeEhiaEVvRDJfZXhCUTNIUnF3YUN5c011VlhPdngxdWZmcWRMM3hfWnlibXdvYWRmYl95WkdSaUw3aFRZUDdFR0FkRjNuQ24zazAxSENzUEtCRGh5TXJ1bW9taG1Mb2ZQdWhucTVZc3VyR3hrNTRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNeEtzdGJ4LU1KT0xsQVE2Yk1ZS2hCQmZzdFdrNjBvMkUyYXdvYTBqTldpanNIRUhDM3RNdGVfVnJxY3JqOWV1TVdUMVVrUjhyczRra29jSTAtejVnRG9YNzBkVVN5czcyTTlJcXR1emJ1Y05XcTl1a0ZBaWRXR0MwMDNteUtITHpPbFBycW5HQWd3YVlyM3VRVkcteEZkeU5palZKLXNvTzVObW1LN1dYUF9hcHJ0WVpoc3dCZGFfenQ2dDBjWTJ3S1d4N21UdUxaVHAzd3BLb3Rtc2M1TjZnZ1EybDhyaHM0aTRQQkVpRENMWGthREJEbXF1dXowdw?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46142.35586805556</v>
+        <v>46142.38166666667</v>
       </c>
     </row>
     <row r="6">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dubai Chamber of Commerce and FedEx discuss supply chain readiness with representatives from 196 companies - ZAWYA</t>
+          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Dubai Chamber of Commerce and FedEx discuss supply chain readiness with representatives from 196 companies - ZAWYA</t>
+          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:09:36 GMT</t>
+          <t>Thu, 30 Apr 2026 07:45:40 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNeEtzdGJ4LU1KT0xsQVE2Yk1ZS2hCQmZzdFdrNjBvMkUyYXdvYTBqTldpanNIRUhDM3RNdGVfVnJxY3JqOWV1TVdUMVVrUjhyczRra29jSTAtejVnRG9YNzBkVVN5czcyTTlJcXR1emJ1Y05XcTl1a0ZBaWRXR0MwMDNteUtITHpPbFBycW5HQWd3YVlyM3VRVkcteEZkeU5palZKLXNvTzVObW1LN1dYUF9hcHJ0WVpoc3dCZGFfenQ2dDBjWTJ3S1d4N21UdUxaVHAzd3BLb3Rtc2M1TjZnZ1EybDhyaHM0aTRQQkVpRENMWGthREJEbXF1dXowdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitANBVV95cUxPNlBJc1JIbVZDUnM5VkVXeXQtb25HQk9qT2JlQjFuOE40Q2ZBQ1hvOUZ5WHBDbGZ0RkZMYUtjOTc0MEpVOHZzNmVuS2tKN1B1bmJSZHlEQXE4Snloc2RYRExTVUhLUU1qVm1wUWpybGxzczlYUU9WXzFmYzBvLVpuQWRBU2g2Y3pMUnQ2cUpfRkdjUTlZYmFOOFRjV0FYM2J3VERBWHZ4Y0hJX29WMVBJYVV0S0Z1TmFKbGFRVTJDSHo1aWxndVRiOHVhem43Ym9ZajJuNWQ2NF9HT3Q2RFZOWml0emYtczFSVHRHbDNmZU9lcm1GLVlwam9MaUJfWXQwMVlZRUMxckx0cWlDeFNhNjRiZ0RNSzJCUHhOd3FfQWgxckcyRDVUdVkwN3k4dl84cXprbnJhRnlPQ3JDNnI5aDlvZWV6bXJPRi12eUhjV0toT2ZHT1FUVF94RFdRN0RaaWw4Z1V1OEpvY2dzSGJWY3JlNUR6NHd6MU4xVUVXTnpTTkRCdGp3V2tWNml6WWd5X1lOSDRGbUw1UDJhSDNUWVNEdUVjYm40OFB0eHU5V0RlejFl?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,38 +749,38 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46142.38166666667</v>
+        <v>46142.32337962963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>Onze man volgde grote politieactie in Antwerpen mee: “Plots ratelt er een knalgele Skoda voorbij... Die werd meteen aan de kant gezet” - HLN</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Amazon rolls out 1-hour and 3-hour delivery options for select items - MSN</t>
+          <t>Our man followed a major police action in Antwerp: “Suddenly a bright yellow Skoda rattles past... It was immediately pulled over” - HLN</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 07:45:40 GMT</t>
+          <t>Thu, 30 Apr 2026 09:41:51 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitANBVV95cUxPNlBJc1JIbVZDUnM5VkVXeXQtb25HQk9qT2JlQjFuOE40Q2ZBQ1hvOUZ5WHBDbGZ0RkZMYUtjOTc0MEpVOHZzNmVuS2tKN1B1bmJSZHlEQXE4Snloc2RYRExTVUhLUU1qVm1wUWpybGxzczlYUU9WXzFmYzBvLVpuQWRBU2g2Y3pMUnQ2cUpfRkdjUTlZYmFOOFRjV0FYM2J3VERBWHZ4Y0hJX29WMVBJYVV0S0Z1TmFKbGFRVTJDSHo1aWxndVRiOHVhem43Ym9ZajJuNWQ2NF9HT3Q2RFZOWml0emYtczFSVHRHbDNmZU9lcm1GLVlwam9MaUJfWXQwMVlZRUMxckx0cWlDeFNhNjRiZ0RNSzJCUHhOd3FfQWgxckcyRDVUdVkwN3k4dl84cXprbnJhRnlPQ3JDNnI5aDlvZWV6bXJPRi12eUhjV0toT2ZHT1FUVF94RFdRN0RaaWw4Z1V1OEpvY2dzSGJWY3JlNUR6NHd6MU4xVUVXTnpTTkRCdGp3V2tWNml6WWd5X1lOSDRGbUw1UDJhSDNUWVNEdUVjYm40OFB0eHU5V0RlejFl?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxORmpFSnhSSTVKRmkwcHJRRkVqSkt0TFZUcllKNnBuU2NQM1c2WjhRQUFvcGpSb0Z4Um1ZRU5Ed1pkaXNfcGhSdGtPZDR1Vnl0M0g1WWNqRFZ5dkxqQXpUQTdHWXR4UFRydzVadEN5MUpkczJYQ1poSWJJckpfaVNTR1YwWjFwMVM2NGV5M1E3Mmw1elZ5cXpGQnE3LVppRUtIT0hQQll6M2MwZ3lIRU1BNVJEY2lONXdfeGQtYm5CRmt4N3dZcjd2aTA0THpvS3VkQW8xSDRnWFRzT0dpRjVtMlhmXzJrLTZLSFBSandsR3JzV1hBQjI2a0FCeDc?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -790,52 +790,52 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46142.32337962963</v>
+        <v>46142.4040625</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Delivery driver in Amazon vest charged after violent rampage in Woodhaven, prosecutors say - Gothamist</t>
+          <t>Verdachte (22) steekpartij Merksplas blijft in de cel - Nieuwsblad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Delivery driver in Amazon vest charged after violent rampage in Woodhaven, prosecutors say - Gothamist</t>
+          <t>Suspect (22) in Merksplas stabbing remains in jail - Nieuwsblad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:00:00 GMT</t>
+          <t>Thu, 30 Apr 2026 13:57:39 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxNTXQwVl96VWhYd0w3WExlVDZOZHZjdjN2czI3aEZXQVpxc3NQOGpkTEE0SjFUaE5fVllhb1k0UlZ0NHQwLTVkMlZxcjhlUFJfYjFDLUNDSGJQb3UzTmZCMDJZWTBIek54NzUtNTgxaHJrRHZDVmZ4ZkR2TnVoSTUwQU4wdFY2QkxTMjh5MGp1a18xdWpPVVd0ekxFR19WSzFsSFpicmhrV1NtVVBPcWYxSENkWmR2YzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxQakhsZG56dEstVWtWTTR6U3FqeUhsaEJvMWZiNUh0ZUpZSWhqeElnMS1wQmlPeGlneUE0RElfMURNYmdIQmpoWWg3VHNuVmZGOTZlYXF5SFZoZ09MazZQVVBtcnQtVklYamtKdjVmYW5uRGdTWS1pWHI4MjBoVHpfRnJLSDFuSTAxU1RTWDNOaGp0ZTFVVXBqamthNGFUWE9ZRy1pZ3JfdkItcjNyb1FSRTROUlRPRUIyYlhROHNGbjBJNXM?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -845,21 +845,21 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46142.41666666666</v>
+        <v>46142.58170138889</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Onze man volgde grote politieactie in Antwerpen mee: “Plots ratelt er een knalgele Skoda voorbij... Die werd meteen aan de kant gezet” - HLN</t>
+          <t>Families van slachtoffers schietpartij op Canadese school klagen OpenAI en CEO Sam Altman aan - GVA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Our man followed a major police action in Antwerp: “Suddenly a bright yellow Skoda rattles past... It was immediately pulled over” - HLN</t>
+          <t>Families of Canadian school shooting victims sue OpenAI and CEO Sam Altman - GVA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:41:51 GMT</t>
+          <t>Thu, 30 Apr 2026 10:46:32 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxORmpFSnhSSTVKRmkwcHJRRkVqSkt0TFZUcllKNnBuU2NQM1c2WjhRQUFvcGpSb0Z4Um1ZRU5Ed1pkaXNfcGhSdGtPZDR1Vnl0M0g1WWNqRFZ5dkxqQXpUQTdHWXR4UFRydzVadEN5MUpkczJYQ1poSWJJckpfaVNTR1YwWjFwMVM2NGV5M1E3Mmw1elZ5cXpGQnE3LVppRUtIT0hQQll6M2MwZ3lIRU1BNVJEY2lONXdfeGQtYm5CRmt4N3dZcjd2aTA0THpvS3VkQW8xSDRnWFRzT0dpRjVtMlhmXzJrLTZLSFBSandsR3JzV1hBQjI2a0FCeDc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxOVDJQS1FsbmZSbHFfODNVVjFNV1VZQl9GWjI0MFJKNS03QzM5SjBydGgwTG5BTHU0YU9VbzZiQmhBZERYVzc3aEROV3A1WXNlbDVMcUpVSEFWVzNiRkY2RWc4X1BGMkFfczcybnp4cC1sc09DeE0wb2E0OTNqMDlsak5RY21vSmNPMTNHVnZfNG9lRTBLWUhhYnJiQ0lLWXRiMzlkNnFBQ2llaVl5b3VHUzNCSmp5Smw3Wll6Y1FHZmFxQVNUTS1seTlPa3JOZ1E5dmgwTA?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46142.4040625</v>
+        <v>46142.44898148148</v>
       </c>
     </row>
     <row r="10">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Families van slachtoffers schietpartij op Canadese school klagen OpenAI en CEO Sam Altman aan - HBVL</t>
+          <t>Veroordeeld tot zes jaar cel: zedendelinquent (37) gearresteerd op het Kiel - Nieuwsblad</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Families of Canadian school shooting victims sue OpenAI and CEO Sam Altman - HBVL</t>
+          <t>Sentenced to six years in prison: sex offender (37) arrested in Kiel - Nieuwsblad</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 12:00:42 GMT</t>
+          <t>Thu, 30 Apr 2026 12:58:32 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1gFBVV95cUxQaHdGMlVkRU9fSlRCRjVDWmJETTgtRmRibWpPNkx4YmFaV2ZmNVJTX25CMkVHaWM5alFZMkFRaTlneDNDR3FyVkhJdjY1VWpwTjFlTnJaYjlTYk50bmtGTW0wUlNpcUt3Y0x2aGdleUVGaGYzczNqQjYzMEM5bTlaRkZWdy1CRDE4VkFjR0pqNFQxYkhKUURmVjkweHl5dGZMTTZXSGJ4MWxrUWFSSFRSV3JxcmM1aVEtM1F6X0thVlZZSS1RV0swXzAxb3M1cUo4bDhvSG1n?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOY3hDYUt5bDdjeEFraFJVN3B1MXo1VXZwd0ZxM0p6d042eVgwd0lVNTZVeDQ2TDdBcDZUMmFrOU5DQm5oN1lncU5yY2ZVblE3ZE4xeXFlaVFoRmtDQjBjb0REdmNtTloySUM3SWxTbzU0WW5UWUt6SzFobl85MXlZajZTZTF2ZERoWXo3TzNteWhnbWhjMGhFeURqRzRiX2h4Rm5EZEI4UGhVdlFxNzZnSGp4ZEd1MmtkT3FoQ19zQ1U3RG1UYzIxNm1FMW9zeENYUU5BWXpnMWM0QndGTmtGd2lLNENSajZiNnJZSzc4VVFiMXZK?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46142.50048611111</v>
+        <v>46142.54064814815</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brits parlement wil 25 miljoen pond extra uitgeven aan veiligheid Joodse gemeenschap - NOS</t>
+          <t>Advocaten Makaveli Linden: “Die man is ziek en moet geïnterneerd worden” - Nieuwsblad</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>British parliament wants to spend an extra 25 million pounds on security of the Jewish community - NOS</t>
+          <t>Lawyers Makaveli Linden: “That man is sick and must be interned” - Nieuwsblad</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:54:30 GMT</t>
+          <t>Thu, 30 Apr 2026 10:08:13 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxNOGM1VU9RX3g2WGpoaHZoMGdGOVZjQnZYOUdTNUpLd3NfMzVuUkpjajVTLXhWZnpKMGlpZFo3UXBZS1dKWXY4OXZxR0ljQmpMV2RVbGhOZS1pTjF2UVpzMmxDdTc3enlyNGZfSGxDeFIxRnNyMXgyZmhVd0tFSW5LbXFmY0ZsWENVZ2lKdko0Q1g5dEJrR0NLZ3laTG0zSjVIbFVDMGtNY0VOaklabjVzaDQxelAtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORl9GaTFrTkg0My01LUdaWmZ2dmRpWGxrMXI2NkpaWFJ6Z0p6S0xXb0d4QU8zYzQ4Y0RRUzRXQjE0MEt6MS1SREZ6TUxKUmJqdU5RcGRtLUJQVnhSemJ6eDB6bzdLdzNNYWNJX284WlQ1NzlfVWw2di0zWXhNWU5DYVQ1Ulh3bE1uM3dwQVdKQ0hia0FzbHVRNWdFemtTYWpSUUZtX25KS3lOMDczWE0yOGlZWFNWMEtvc0k4TlBxSTZmd2ZHUzdmcWhBMmNiZVBJYnpwelQ0VzM0cWlQOWVhRnpYLVAydw?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,38 +1024,38 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46142.45451388889</v>
+        <v>46142.42237268519</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Advocaten Makaveli Linden: “Die man is ziek en moet geïnterneerd worden” - Nieuwsblad</t>
+          <t>Deadzoning travel trend sees travellers switch off for wellbeing - Travel Tomorrow</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lawyers Makaveli Linden: “That man is sick and must be interned” - Nieuwsblad</t>
+          <t>Deadzoning travel trend sees travellers switch off for wellbeing - Travel Tomorrow</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:08:13 GMT</t>
+          <t>Thu, 30 Apr 2026 07:58:10 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxORl9GaTFrTkg0My01LUdaWmZ2dmRpWGxrMXI2NkpaWFJ6Z0p6S0xXb0d4QU8zYzQ4Y0RRUzRXQjE0MEt6MS1SREZ6TUxKUmJqdU5RcGRtLUJQVnhSemJ6eDB6bzdLdzNNYWNJX284WlQ1NzlfVWw2di0zWXhNWU5DYVQ1Ulh3bE1uM3dwQVdKQ0hia0FzbHVRNWdFemtTYWpSUUZtX25KS3lOMDczWE0yOGlZWFNWMEtvc0k4TlBxSTZmd2ZHUzdmcWhBMmNiZVBJYnpwelQ0VzM0cWlQOWVhRnpYLVAydw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0hkRXNwcDRrUW9obmlpWnRZQjcwNGF1S1hXVWJ3ZzBka2RWTWRibU9lZzFCclV0OUZHQ0IzWEJ0WVQwZ21oM0lNR1pNMldoY3FEaE5XNlE4WjVTbGlPdmxTZzczTHhteTlFbVVYRjlGcHVvUlgwUzNBQTBobFJMSzI1WkgzdzBPSGlOWnhrZF85WGNLMk9V?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1075,11 +1075,11 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46142.42237268519</v>
+        <v>46142.33206018519</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Deadzoning travel trend sees travellers switch off for wellbeing - Travel Tomorrow</t>
+          <t>Brussels for kids: What to do with your family this weekend – 1 to 3 May - The Brussels Times</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Deadzoning travel trend sees travellers switch off for wellbeing - Travel Tomorrow</t>
+          <t>Brussels for kids: What to do with your family this weekend – 1 to 3 May - The Brussels Times</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 07:58:10 GMT</t>
+          <t>Thu, 30 Apr 2026 09:35:12 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0hkRXNwcDRrUW9obmlpWnRZQjcwNGF1S1hXVWJ3ZzBka2RWTWRibU9lZzFCclV0OUZHQ0IzWEJ0WVQwZ21oM0lNR1pNMldoY3FEaE5XNlE4WjVTbGlPdmxTZzczTHhteTlFbVVYRjlGcHVvUlgwUzNBQTBobFJMSzI1WkgzdzBPSGlOWnhrZF85WGNLMk9V?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUzJvWFB0LWFtdUNjTlcwYWpjREdtOGRxRGpQSnQ1dHU4WWR6V1Q5c21ocW5iQjExNExxeXNVOE1vV0JBMURnRHdDRFhZU0d6SEJHWUR1cmZEMVVxZlBFeDJMZThTR09BRmNibERGc3hsOVdPUzVleE5SM1FEc2IxZ1RRY2VsTDFIUmJpYkllMHlrVHZzeG43M2RfMEJiNmliX3JUcThIMFJjRTQ?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46142.33206018519</v>
+        <v>46142.39944444445</v>
       </c>
     </row>
     <row r="14">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brussels for kids: What to do with your family this weekend – 1 to 3 May - The Brussels Times</t>
+          <t>Raouna condemns antisemitic attacks in Europe in address to European Parliament | Cyprus inform - Cyprus Inform</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Brussels for kids: What to do with your family this weekend – 1 to 3 May - The Brussels Times</t>
+          <t>Raouna condemns antisemitic attacks in Europe in address to European Parliament | Cyprus inform - Cyprus Inform</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:35:12 GMT</t>
+          <t>Thu, 30 Apr 2026 09:21:49 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxPUzJvWFB0LWFtdUNjTlcwYWpjREdtOGRxRGpQSnQ1dHU4WWR6V1Q5c21ocW5iQjExNExxeXNVOE1vV0JBMURnRHdDRFhZU0d6SEJHWUR1cmZEMVVxZlBFeDJMZThTR09BRmNibERGc3hsOVdPUzVleE5SM1FEc2IxZ1RRY2VsTDFIUmJpYkllMHlrVHZzeG43M2RfMEJiNmliX3JUcThIMFJjRTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQUWh4LXBkT2VsYjFBVXZlcmpaS2hjd3ZXc1NiN0wzV1pPOUFpUVVfeURoZXpfRi12aTVya2txdWFVNWVObm9UVkE1c3JpN1pmZXBJeVFPR01DMnRMMWVGSVNOWU9Ecmk4WGRyQUlIQXEzM0ZUbW9MbjB4amNTYmVZdUxKRllHNGFZTDd5WURGSkI4Y004dHktckpya3YzT0FuWWpnRnZybmJuS3VEbDJ6NXNtRkt5ZzJDX0JxLW82RdIBxAFBVV95cUxNUE40Z2I3b3c1VWpBUUdBVDFMNUMwUEI2U0NydUQ5ZmhpTWQwSXB6eGZKc09GRkpLRGlxb1EtOEk5YzZuajd0aUVRYWFpS1RTLWVVa0s2LWE3dDZmUDBZZE91VjlwVUE4Y2gxcTJNVklMZVhHbFZvQ0R2Xy1OOF9UaUpESVIzWWxBQ0U0YUx4S1ZYLWpnbl9xRnk1aVlsTFd5UXg0bE96aEVCSGVSN2Vja2Y0OTRlalBnWGI1YXh5emhRV1pk?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,38 +1189,38 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46142.39944444445</v>
+        <v>46142.39015046296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium English (fallback)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Maasmechelen" OR "Genk" OR "Hasselt" OR "E314")</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Raouna condemns antisemitic attacks in Europe in address to European Parliament | Cyprus inform - Cyprus Inform</t>
+          <t>Next Chelsea manager given £41m welcoming gift as BlueCo transfer gamble pays off - Football London</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Raouna condemns antisemitic attacks in Europe in address to European Parliament | Cyprus inform - Cyprus Inform</t>
+          <t>Next Chelsea manager given £41m welcoming gift as BlueCo transfer gamble pays off - Football London</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:21:49 GMT</t>
+          <t>Thu, 30 Apr 2026 12:34:37 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivwFBVV95cUxQUWh4LXBkT2VsYjFBVXZlcmpaS2hjd3ZXc1NiN0wzV1pPOUFpUVVfeURoZXpfRi12aTVya2txdWFVNWVObm9UVkE1c3JpN1pmZXBJeVFPR01DMnRMMWVGSVNOWU9Ecmk4WGRyQUlIQXEzM0ZUbW9MbjB4amNTYmVZdUxKRllHNGFZTDd5WURGSkI4Y004dHktckpya3YzT0FuWWpnRnZybmJuS3VEbDJ6NXNtRkt5ZzJDX0JxLW82RdIBxAFBVV95cUxNUE40Z2I3b3c1VWpBUUdBVDFMNUMwUEI2U0NydUQ5ZmhpTWQwSXB6eGZKc09GRkpLRGlxb1EtOEk5YzZuajd0aUVRYWFpS1RTLWVVa0s2LWE3dDZmUDBZZE91VjlwVUE4Y2gxcTJNVklMZVhHbFZvQ0R2Xy1OOF9UaUpESVIzWWxBQ0U0YUx4S1ZYLWpnbl9xRnk1aVlsTFd5UXg0bE96aEVCSGVSN2Vja2Y0OTRlalBnWGI1YXh5emhRV1pk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxNYmRQamE3OEc5Q18tM3pKRHl6N3kwM3NtOHVVS09GLUFXU3V1Z3VEaFJpc1BXQWg4V1llSkh6NFNZa0x3elNBOFYxNjJESmFOUmFKZmdVZmhpMlVKNmRRbnVUU21ZdFFzZjN3dUtqeVlFS09BTUhyRUpvN2Z2MVN5dW9BRWhRd0hzSWNEaERJRk3SAZABQVVfeXFMTWJkUGphNzhHOUNfLTN6SkR5ejd5MDNzbTh1VUtPRi1BV1N1dWd1RGhSaXNQV0FoOFdZZUpIejRTWWtMd3pTQThWMTYyREphTlJhSmZnVWZoaTJVSjZkUW51VFNtWXRRc2Yzd3VLanlZRUtPQU1IckVKbzdmdjFTeXVvQUVoUXdIc0ljRGhESUZN?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,7 +1244,7 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46142.39015046296</v>
+        <v>46142.52403935185</v>
       </c>
     </row>
     <row r="16">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Overlast Overkophuis Maasmechelen zorgt weer voor ophef: “Sommige jongeren trekken nu liever naar Lanaken” | Foto - HLN</t>
+          <t>Gezondheidszorg staat bovenaan klachtenlijstje: “onmenselijke” situaties in overbevolkte gevangenis in Hasselt - Nieuwsblad</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Nuisance Overkophuis Maasmechelen is causing a stir again: “Some young people now prefer to move to Lanaken” | Photo - HLN</t>
+          <t>Healthcare is at the top of the complaints list: “inhumane” situations in overcrowded prison in Hasselt - Nieuwsblad</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 08:14:06 GMT</t>
+          <t>Thu, 30 Apr 2026 13:47:10 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNVzZrekZ3cXRVN1d6cEN5cm9PUHNubXYzSGpvSnN5dmF0NmRsNGoyeEVhVW5fLWc5S196NGljdW10LXE4VkxQRXNYc3R6V21VSVBBZ3ZzMkRUbWNhY3ByZ3Z3dFF6NllId0VBSC1NOGpOeXRzQ3pfNTFPalJWYUdWS1JVa3VwQVhEc2haa19ka2E0YUV3YUkzQjRNQ2xXWVJ6TU9OdTJSdGtCTnpiSnQyWjFBSjdCcFdjZ3JaS0VZazNJV21WdFNIazhWaFYteGo0VDVKTU5PT3RxYjVXbW5IQWZqN25ZMzRVTEpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNZ2JnZlp4RVZ3VTJqcFhPd2RZVmx0UjdFTFRYWkd3SEpVQVZLeURsNTEtY3p6UEo3ZE1raHpyNEFlb1FjMnJVTmEyZkpsd2RXT3Z2MEptcG5HdDZSbVB1MDUwMTNsY01xLVl4SkE1ZVE2ejhJX2hYMHpwZGEtMm9rVDJOa21uZVd3TnNZVkllVnVLOVp6dGdUeDltcWNkR2N5YmhoUTVVTVQ1V2gzaHFudmZZbzAwd1g3NXZDLU9sTndfSGo4R0tNeXVnXzFrRWtmcmRfc0R0Slg0Y1duNU16QTVjYi02ams2MGIxbEprU18?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46142.343125</v>
+        <v>46142.5744212963</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hasseltse gedetineerden kunnen niet fatsoenlijk eten door tandpijn - HBVL</t>
+          <t>Overlast Overkophuis Maasmechelen zorgt weer voor ophef: “Sommige jongeren trekken nu liever naar Lanaken” | Foto - HLN</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hasselt detainees cannot eat properly due to toothache - HBVL</t>
+          <t>Nuisance Overkophuis Maasmechelen is causing a stir again: “Some young people now prefer to move to Lanaken” | Photo - HLN</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 12:11:08 GMT</t>
+          <t>Thu, 30 Apr 2026 08:14:06 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxOS1d2VExxTVR1RFJJa1BHU252SDZTNXdBOUtvRV9zVkdQSksyZGxHN0o0QnRqVlNpM3ViOHNoZjhjdDdidHZ4LTg4QUF0Vy1rYnYzOVVpSTJZbzBzMk1pX1U0MVlMQVZIWGM3WGRPeFpudUcyVFBOOFJiVFI3cmVZZFpwajJaX1VVQVo3SXJOZ0o1THMyTEJDSjMxZWhwUXBnbVd0ckhaaEl1Q3QzTjdnOVN5bWtmdms0VU1TcmFfZVM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNVzZrekZ3cXRVN1d6cEN5cm9PUHNubXYzSGpvSnN5dmF0NmRsNGoyeEVhVW5fLWc5S196NGljdW10LXE4VkxQRXNYc3R6V21VSVBBZ3ZzMkRUbWNhY3ByZ3Z3dFF6NllId0VBSC1NOGpOeXRzQ3pfNTFPalJWYUdWS1JVa3VwQVhEc2haa19ka2E0YUV3YUkzQjRNQ2xXWVJ6TU9OdTJSdGtCTnpiSnQyWjFBSjdCcFdjZ3JaS0VZazNJV21WdFNIazhWaFYteGo0VDVKTU5PT3RxYjVXbW5IQWZqN25ZMzRVTEpB?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46142.50773148148</v>
+        <v>46142.343125</v>
       </c>
     </row>
     <row r="23">
@@ -1645,22 +1645,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tuinbrand in Hasselt beschadigt appartementen - TV Limburg</t>
+          <t>Bakker opnieuw open na hercontrole van FAVV: “We gaan de zaak wel opvolgen” - HBVL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Garden fire in Hasselt damages apartments - TV Limburg</t>
+          <t>Bakker reopens after re-inspection by FAVV: “We will follow up on the matter” - HBVL</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:44:47 GMT</t>
+          <t>Thu, 30 Apr 2026 08:56:08 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOTEx6Vk9YdUEzeENGRTI5c28zd0N5Sk5ucndnY29wZVhKX1h1RTdGUFE3YUo5ZjhsWm1IOWF3VG9WbXpPZjhWTWdZM1VlNXIzWkQwYUxFdWlFSEY0bnB5WnRWTWF3M29VZmN6NW1RalVvcUJ0eWk1MXhNRXJ0UGxGcnYzeC0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AFBVV95cUxNb2x3Q1hoS01KV2lIS3RuY2ZZRGdPbThWYzVBU2ZyeUdwV0ZxU2JGQUV2YUIzMks2M09rV1FHQWtEM2ZMMnN2ZjlRclBBSkFPOFhid09SSHdSZnhXeFFCelJvaG5tLVY3VnExWEJUREFtLXNGLWgwX2ZPUkJsT0ZsZnJsTXlXU3RNSFI5YzVqeldTOFptQ2IwSTR0d1F5SUZBYjF1aHFPNVJlbzdlV2pKQ2pZeDJaVDYyRjBfZ1lhcGJJWFg1WU16clJQMTdmX3FuQmdhZ1RVeFY?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46142.4477662037</v>
+        <v>46142.37231481481</v>
       </c>
     </row>
     <row r="24">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bakker opnieuw open na hercontrole van FAVV: “We gaan de zaak wel opvolgen” - HBVL</t>
+          <t>Tuinbrand in Hasselt beschadigt appartementen - TV Limburg</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Bakker reopens after re-inspection by FAVV: “We will follow up on the matter” - HBVL</t>
+          <t>Garden fire in Hasselt damages apartments - TV Limburg</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:08:44 GMT</t>
+          <t>Thu, 30 Apr 2026 10:44:47 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizwFBVV95cUxPWmRBUUFmb2RHLTBEdEpKaDYwVU15OGZwM3RWVEJBdjAwWloyR2dNSWxyMy14cndWY3J6UWRlbDBZcUl0d21NczBfXzBaYU0zYXA3QVVseldmSkdoWkZCSEFRd3ktOC1IZU1yeDY3MFk3YVMxd2x4aGtYeUJwc1YteU5KeldtbmotSFI2X1FtZUpXZTJPQUtDbDBzSkROU3UzcTFfemJ3aXA2eU1paEs4NDdKN2RkYzc5dHhpM1FwM1gyemVBRUZJNHE0ZVVVQUU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxOTEx6Vk9YdUEzeENGRTI5c28zd0N5Sk5ucndnY29wZVhKX1h1RTdGUFE3YUo5ZjhsWm1IOWF3VG9WbXpPZjhWTWdZM1VlNXIzWkQwYUxFdWlFSEY0bnB5WnRWTWF3M29VZmN6NW1RalVvcUJ0eWk1MXhNRXJ0UGxGcnYzeC0?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46142.38106481481</v>
+        <v>46142.4477662037</v>
       </c>
     </row>
     <row r="25">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Buslijn 66 blijft behouden, maar krijgt aanpassing. - HLN</t>
+          <t>En plots lig je met Dina Tersago in bed: opvallende campagne bij Ikea Hasselt vraagt aandacht voor pleegzorg - HLN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Bus line 66 will be retained, but will be adapted. - HLN</t>
+          <t>And suddenly you're in bed with Dina Tersago: striking campaign at Ikea Hasselt draws attention to foster care - HLN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:18:35 GMT</t>
+          <t>Thu, 30 Apr 2026 13:53:35 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQTmMzMjRyRjVoRS1URVY0eW5yTVhYS1N4bkJIbFluQmdHbnAyREcyQ0FPUWlaeUlSQng3VTVPTV9nWkVsWDNEZHVZSUxja19jX2pJaFhneG0wZXBOSkNuZEdxZFZXNmk3SXJFVmg4b2ZzWlJCVF9fMHIwZUdqX2xLQUFRZVFCLVplUHk3RmViWQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxNbWxBYjdacWdsa0RCdFBIeDNkdXRFWjVmampGSlVnWW9PR09mNFhVT0Nnbzd3bExHSHJZd2NiVFlXbUZxc196WHZWRERXVkkzc2hmMEg3ZlRVMVNGTWhzWXJ4UDJTYU05RkpfUE04c25sRThFRHAydE43MXFRNmx4dVhjdjJtaUpPSHdwUEhmeWFUeExZUEMxUkV0RmFqZ1RIWjE5ZnZNTHJ2SXlERmh4RDJWc1BpNHMwTjBvUmZBT0g1U3kzZkV3dFUtUTAwSEoteEFKdWZ1VGRzUHZs?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46142.42957175926</v>
+        <v>46142.57887731482</v>
       </c>
     </row>
     <row r="26">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>22-jarige dakwerker blijft verkeersregels negeren: “Hij is een product van een vechtscheiding” - HLN</t>
+          <t>Buslijn 66 blijft behouden, maar krijgt aanpassing. - HLN</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22-year-old roofer continues to ignore traffic rules: “He is a product of a divorce battle” - HLN</t>
+          <t>Bus line 66 will be retained, but will be adapted. - HLN</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:08:31 GMT</t>
+          <t>Thu, 30 Apr 2026 10:18:35 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPMUJxYnJKTE5jX2RTdy1nTFVtTmVGZFplbkdiSXFWVFRCYnBhekpzR2tQNVo0MUVyRzY4THJNYmtQLWdUQllaV1czLUZTY3pQZkwyOWd2VllMVGk3ZnJZMzQtV0k1d1E0aWhBeHgyZFpnOUJuM0UyWDJjS1h2czNwTF90dTFWSUJvODdfc3dfU3Qtb0VwRG9YOElfZngzelBaak10SlA3RXlJNlczanFKM2lHZW9sekJJamQtcXJXTDdtQjREZWN3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxQTmMzMjRyRjVoRS1URVY0eW5yTVhYS1N4bkJIbFluQmdHbnAyREcyQ0FPUWlaeUlSQng3VTVPTV9nWkVsWDNEZHVZSUxja19jX2pJaFhneG0wZXBOSkNuZEdxZFZXNmk3SXJFVmg4b2ZzWlJCVF9fMHIwZUdqX2xLQUFRZVFCLVplUHk3RmViWQ?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46142.46424768519</v>
+        <v>46142.42957175926</v>
       </c>
     </row>
     <row r="28">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>208 klachten, 48 grondslapers en tandpijn behandeld met paracetamol: rapport legt ‘onmenselijke toestand’ in Hasseltse gevangenis bloot - HLN</t>
+          <t>22-jarige dakwerker blijft verkeersregels negeren: “Hij is een product van een vechtscheiding” - HLN</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>208 complaints, 48 ​​floor sleepers and toothache treated with paracetamol: report exposes 'inhumane condition' in Hasselt prison - HLN</t>
+          <t>22-year-old roofer continues to ignore traffic rules: “He is a product of a divorce battle” - HLN</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:16:29 GMT</t>
+          <t>Thu, 30 Apr 2026 11:08:31 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPdzN1WEVkRnVKc1lmU0M0UUc2RFYyUTFzRjZlOVp3ZW9NVnpIYmpQTER3UDB3MkgxbkpFMlljTjRaRzdhbGF1SWcteTJyc0tvd1VBMXpmbVlqMmhOalg0NTFrMmlPNFhYTUZnLVhidExzZUhQdUp3eWw4dmtoNXIyQUdpd2Y3ZTd1ZHRXZFFZMHpQRzVmalVsa0R1aE1rNUFwcTNXeEVLUm9XdzR3Q0NTdmFlMlV3TlFxRlhzXzE2Y01sRWV2eFBfMmNEdlRZRDI4T3ZsMG5tQmtoam5WZlV6QVhLQ3lKR3Qxa0dsR0RwYTAzLVlLTUJhY0pIZlg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixwFBVV95cUxPMUJxYnJKTE5jX2RTdy1nTFVtTmVGZFplbkdiSXFWVFRCYnBhekpzR2tQNVo0MUVyRzY4THJNYmtQLWdUQllaV1czLUZTY3pQZkwyOWd2VllMVGk3ZnJZMzQtV0k1d1E0aWhBeHgyZFpnOUJuM0UyWDJjS1h2czNwTF90dTFWSUJvODdfc3dfU3Qtb0VwRG9YOElfZngzelBaak10SlA3RXlJNlczanFKM2lHZW9sekJJamQtcXJXTDdtQjREZWN3?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46142.46978009259</v>
+        <v>46142.46424768519</v>
       </c>
     </row>
     <row r="29">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Buitenbad Kapermolen klaar voor zomer na herstellingen: “1,5 miljoen liter water in vijf dagen gevuld” - HLN</t>
+          <t>208 klachten, 48 grondslapers en tandpijn behandeld met paracetamol: rapport legt ‘onmenselijke toestand’ in Hasseltse gevangenis bloot - HLN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Kapermolen outdoor pool ready for summer after repairs: “1.5 million liters of water filled in five days” - HLN</t>
+          <t>208 complaints, 48 ​​floor sleepers and toothache treated with paracetamol: report exposes 'inhumane condition' in Hasselt prison - HLN</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 08:43:29 GMT</t>
+          <t>Thu, 30 Apr 2026 11:16:29 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQY3hTVUFad0lOYkZYVGxUU0tmU29sRmhacjlLWTdCRGxtTWs0YXE0RXdIbmRMS0VZeXk4bWVMTEtvNklkOV9fNWVhMldLQzN2OEdxMUYtN3NhUUFaUC0wWlFZaTVVOWZGakhEc3o2clcwY0dTOTFCYzFrSzRBS3hONlk5UkZpMFIzdDc4TDVsYUJKM0ttNjQ5aVYzSE5Gbm5wazd5VUt2MjdvV0ZvU2hBdnRLYkh5dHlOR2hyUmk0eW16R1ljekNPVi0xNm9nYWJPdlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPdzN1WEVkRnVKc1lmU0M0UUc2RFYyUTFzRjZlOVp3ZW9NVnpIYmpQTER3UDB3MkgxbkpFMlljTjRaRzdhbGF1SWcteTJyc0tvd1VBMXpmbVlqMmhOalg0NTFrMmlPNFhYTUZnLVhidExzZUhQdUp3eWw4dmtoNXIyQUdpd2Y3ZTd1ZHRXZFFZMHpQRzVmalVsa0R1aE1rNUFwcTNXeEVLUm9XdzR3Q0NTdmFlMlV3TlFxRlhzXzE2Y01sRWV2eFBfMmNEdlRZRDI4T3ZsMG5tQmtoam5WZlV6QVhLQ3lKR3Qxa0dsR0RwYTAzLVlLTUJhY0pIZlg?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46142.3635300926</v>
+        <v>46142.46978009259</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>“Gegokt en verloren?”: bestuurder trekt remorque zonder het juiste rijbewijs na evenement op Circuit Zolder - HLN</t>
+          <t>Buitenbad Kapermolen klaar voor zomer na herstellingen: “1,5 miljoen liter water in vijf dagen gevuld” - HLN</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>“Gambled and lost?”: driver pulls brakes without the correct driver's license after an event at Circuit Zolder - HLN</t>
+          <t>Kapermolen outdoor pool ready for summer after repairs: “1.5 million liters of water filled in five days” - HLN</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:53:29 GMT</t>
+          <t>Thu, 30 Apr 2026 08:43:29 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOVWw1MDhkOFlBSkJNdjgtTnBNZlFQdVZlcmpONnBfMkRsaDdMbHZXTEZUSVVoMUFfSGNsX2hqQ1F0U0JGbWo3RmYxMFpUdmlibU44TU5ZdkJiMkxBYlVIVENnSW16M05BMUY2VWFOWlhxbTBwUmlOSXBtNHIyMTNnTzVEQklvdXpYaVNfT1Ruc0psOXAybFJyRmxmMlA3LThPYU9HYm12WHVHaUtWQlUwbGRyOWRyRHExYXZlMkpCUWpVaGw0c3hPb3lwSC11bFczWlEwYm5aUTUtMGRG?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxQY3hTVUFad0lOYkZYVGxUU0tmU29sRmhacjlLWTdCRGxtTWs0YXE0RXdIbmRMS0VZeXk4bWVMTEtvNklkOV9fNWVhMldLQzN2OEdxMUYtN3NhUUFaUC0wWlFZaTVVOWZGakhEc3o2clcwY0dTOTFCYzFrSzRBS3hONlk5UkZpMFIzdDc4TDVsYUJKM0ttNjQ5aVYzSE5Gbm5wazd5VUt2MjdvV0ZvU2hBdnRLYkh5dHlOR2hyUmk0eW16R1ljekNPVi0xNm9nYWJPdlE?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46142.41214120371</v>
+        <v>46142.3635300926</v>
       </c>
     </row>
     <row r="31">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Vintage Chroom Meeting: terug van weggeweest - HLN</t>
+          <t>“Gegokt en verloren?”: bestuurder trekt remorque zonder het juiste rijbewijs na evenement op Circuit Zolder - HLN</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vintage Chrome Meeting: back - HLN</t>
+          <t>“Gambled and lost?”: driver pulls brakes without the correct driver's license after an event at Circuit Zolder - HLN</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:28:35 GMT</t>
+          <t>Thu, 30 Apr 2026 09:53:29 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTlE0RGRHa3p4ZW1FX1B2U3F6d0RUdU1wb1k0LWk2bWIzdmROd1F2X3ZXcWZYUDZDb3pzc0tfdDZsc3N3M2FuTlRTY3RwTkJVS29KZEhqWDhwVS1DUU1IaExMTFBtWHBuYkctZmp1VDk5cUthNTBHUmVGUXlWQW1zVGE5a3h1Y28?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3AFBVV95cUxOVWw1MDhkOFlBSkJNdjgtTnBNZlFQdVZlcmpONnBfMkRsaDdMbHZXTEZUSVVoMUFfSGNsX2hqQ1F0U0JGbWo3RmYxMFpUdmlibU44TU5ZdkJiMkxBYlVIVENnSW16M05BMUY2VWFOWlhxbTBwUmlOSXBtNHIyMTNnTzVEQklvdXpYaVNfT1Ruc0psOXAybFJyRmxmMlA3LThPYU9HYm12WHVHaUtWQlUwbGRyOWRyRHExYXZlMkpCUWpVaGw0c3hPb3lwSC11bFczWlEwYm5aUTUtMGRG?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46142.39484953704</v>
+        <v>46142.41214120371</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>De ene BV-voetbalclub duikt diep in het rood, de andere zit er warmpjes in: “Ik heb nog nooit een euro gevraagd” - HBVL</t>
+          <t>Vintage Chroom Meeting: terug van weggeweest - HLN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>One BV football club is deeply in the red, the other is warm: “I have never asked for a euro” - HBVL</t>
+          <t>Vintage Chrome Meeting: back - HLN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 07:16:37 GMT</t>
+          <t>Thu, 30 Apr 2026 09:28:35 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNeElsNTBOOERoVFItWVBoVWNGZXU5LTQyR0Q3R01WV2JfNTlRV2xpb1c4U0FTbmhLbUhvbnY4UEdxdVQ4LW9hTHNqZ1dmRUM4b2dEc1ZzbkRDaXhpT1N6UHZyWTYtOEhkb1NoclJwVnlJa1BJMThweWlTS2Q5Q1BZdTFoSkdadTJpWHNqenRBcFNnODRENTRWekdzOUppY2l4RHZGcjhMRF9MczNCbmZfMkt3ZGJ4U2lfYmhvZmc2TXE0djJfT3VzNnBLZUJhbHcwN0VoRHRvRE5UUWJVZXBXS0EyMkVWTlVzX19RSF9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxQTlE0RGRHa3p4ZW1FX1B2U3F6d0RUdU1wb1k0LWk2bWIzdmROd1F2X3ZXcWZYUDZDb3pzc0tfdDZsc3N3M2FuTlRTY3RwTkJVS29KZEhqWDhwVS1DUU1IaExMTFBtWHBuYkctZmp1VDk5cUthNTBHUmVGUXlWQW1zVGE5a3h1Y28?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46142.30320601852</v>
+        <v>46142.39484953704</v>
       </c>
     </row>
     <row r="33">
@@ -2195,22 +2195,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Diefstal van Plopworst en agressie op Lijnbus leveren Hasseltse straf met uitstel op - Nieuwsblad</t>
+          <t>De ene BV-voetbalclub duikt diep in het rood, de andere zit er warmpjes in: “Ik heb nog nooit een euro gevraagd” - HBVL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Theft of Plopworst and aggression on Lijnbus result in Hasselt's suspended sentence - Nieuwsblad</t>
+          <t>One BV football club is deeply in the red, the other is warm: “I have never asked for a euro” - HBVL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:53:36 GMT</t>
+          <t>Thu, 30 Apr 2026 07:16:37 GMT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQQ21uMThGSlRoNUlFOVdSRkNsX0E2eDlnU1lDUjhaa1ZhTTRoRlBpSmNYUERtNE9iVDhCX0xBVGhMdjk5eHc3ODY4YUxva211UWJyYjIxYzF5WEk2U1l1WXZySEtJQjVxek5zVnRSSmZzT055NXBlbGktbHktWDFRallGYUpnaTJvOFZ6RDN1WGZkcEJneTY4cmhGeFpla1J2S3JlN2dSdXpEV1A2OV9BVlZRclBhMC1tYmNJYUpveWNnNlBNYlNzZ0J1RzlTSHVTaF9DWkhwZWJEcFY0R01peg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxNeElsNTBOOERoVFItWVBoVWNGZXU5LTQyR0Q3R01WV2JfNTlRV2xpb1c4U0FTbmhLbUhvbnY4UEdxdVQ4LW9hTHNqZ1dmRUM4b2dEc1ZzbkRDaXhpT1N6UHZyWTYtOEhkb1NoclJwVnlJa1BJMThweWlTS2Q5Q1BZdTFoSkdadTJpWHNqenRBcFNnODRENTRWekdzOUppY2l4RHZGcjhMRF9MczNCbmZfMkt3ZGJ4U2lfYmhvZmc2TXE0djJfT3VzNnBLZUJhbHcwN0VoRHRvRE5UUWJVZXBXS0EyMkVWTlVzX19RSF9B?oc=5</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2234,38 +2234,38 @@
         </is>
       </c>
       <c r="K33" s="1" t="n">
-        <v>46142.41222222222</v>
+        <v>46142.30320601852</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Local Town Wertheim German</t>
+          <t>Local Town Maasmechelen Dutch (fallback)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "A3" OR "A81" OR "Würzburg" OR "Aschaffenburg") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz OR Verzögerung) AND -Wetter AND -Sport</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Würzburg: Unfall mit Motorrad, Auto und Bus - Radio Gong Würzburg</t>
+          <t>Diefstal van Plopworst en agressie op Lijnbus leveren Hasseltse straf met uitstel op - Nieuwsblad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Würzburg: Accident with a motorcycle, car and bus - Radio Gong Würzburg</t>
+          <t>Theft of Plopworst and aggression on Lijnbus result in Hasselt's suspended sentence - Nieuwsblad</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 06:59:00 GMT</t>
+          <t>Thu, 30 Apr 2026 09:53:36 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOdGtfRjhBa1VCUUpzcUdfWHRpNllEbWlEVG5oV0F4aVFkdVhneUdaVGdQdEZxeE1OMVdlcU12dW1YZ093UUI4TVZjanBrbjlhUmoxSHV2anIxeTFCRVJENGJMTTZWMUJxLV9iV2NiV19EM1c5TUJjTnlweGZPaGhWR1dR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxQQ21uMThGSlRoNUlFOVdSRkNsX0E2eDlnU1lDUjhaa1ZhTTRoRlBpSmNYUERtNE9iVDhCX0xBVGhMdjk5eHc3ODY4YUxva211UWJyYjIxYzF5WEk2U1l1WXZySEtJQjVxek5zVnRSSmZzT055NXBlbGktbHktWDFRallGYUpnaTJvOFZ6RDN1WGZkcEJneTY4cmhGeFpla1J2S3JlN2dSdXpEV1A2OV9BVlZRclBhMC1tYmNJYUpveWNnNlBNYlNzZ0J1RzlTSHVTaF9DWkhwZWJEcFY0R01peg?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2275,52 +2275,52 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46142.29097222222</v>
+        <v>46142.41222222222</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Local Town Maasmechelen English (fallback)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Scheinbar religiöse Rituale: Angebliche Wahrsagerin betrügt Frau um mehr als 100.000 Euro - Neue Presse Coburg</t>
+          <t>Lori Harvey says she's 'about to have so much fun suing y'all' amid Damson Idris split rumors - MSN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Apparently religious rituals: Alleged fortune teller cheats woman out of more than 100,000 euros - Neue Presse Coburg</t>
+          <t>Lori Harvey says she's 'about to have so much fun suing y'all' amid Damson Idris split rumors - MSN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:35:49 GMT</t>
+          <t>Thu, 30 Apr 2026 11:25:14 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPUG43ZGxYWi1Na3RPdnFBWEVpS3lIRTI3NGpNcUxQSF8yZjI3QnpQaGZQWGFvUERyTGhaOTAzTF9lQW42RUJIVnJaR2ozTzNMV2l2bHhldXZrSE1Nc2hCWDZ6WDNsRlJpT0daSlFKc0tuVi1fV1lBXzg2QzFhTVdHREJueF9Vd3lJcS0tdWxjMC1xRzE5dlE4Qm81bVRxcHZmRGNnckpVT2ZaOEsxbEl3T3pNc1NKUmF4Q2NwM29Uc3Jidy1mUFJldTU4NzRxUFlhYnpxZWZudUVha1NLS05KNEExa29kYm5fdXcydERNamZyLTdHOUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisANBVV95cUxNUFZ5MnlxVDhpNzBXUmJseE5IOElUbk4xUFJKNy1VRnFKRFZubjBoOXJfbHlreDdLZWV0UzEwM2VpRzM4d2N6Y0dLNlZUNFZGbWdIS2N0RHJEYkVJVnQ2cXRDelFfNzRUMHNBY3AxWVVkOVgzalJfWFhqS0R0WGFqYUhCRTk3UEpDR0lLZGkyOFhUS0IxRjFQeXpyT3RlTW9TRlcxYnNjakFLemlwWGhoQW9sVklsU0NlYWNFWmhpaVF5Zkk0WTltZlpOc1o0d3ctbi1YYWpoMXU0QnktNmQxOEU2WTVhakdGZmZsaThjb0dGWEpLMnlIUVBvSVFFZ1hUN185dzhlNjhoNUI4U3djUjlaclpQdkRhWlpHdkxnYUZOUS1ETWlNWlNoX2g4VVNndUo1d1ZkUzc4Z2F2bVRwNVp3OVZFZ0dUb1d2ZzFGOHZWLUJIbU5ZSkpMUUVId0M2YWdxZjlRZ3dRdHhuYm1CV1NNeEVDclU4RVBUN3E3eHpNa2x0dHA4RDhtdXZDY0hQZ3F5OXVoeGx2c25RNHVGQ1ZjVTlBTGhMZktKNFNSbjA?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2330,52 +2330,52 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46142.48320601852</v>
+        <v>46142.47585648148</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>57 Jahre alte Radlerin schwer verletzt bei Frontal-Kollision mit Pkw in Ingolstadt - Pfaffenhofen Today</t>
+          <t>Mystery as billionaire socialite is found dead inside her cabin on luxurious cruise ship - MSN</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>57-year-old cyclist seriously injured in head-on collision with car in Ingolstadt - Pfaffenhofen Today</t>
+          <t>Mystery as billionaire socialite is found dead inside her cabin on luxurious cruise ship - MSN</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 12:19:11 GMT</t>
+          <t>Thu, 30 Apr 2026 07:29:24 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1oMkRHS0prYlgzZXVLdGxUUFBHdGowWkJkWk53b2d1X1ZiX2dfdGs5Rm1qc0FMOUgzMi1sSXF1bjM5azVfTUcwYlQ3azItaTB5SUVyWEpzbXpyY2hoWVRLcUM0dHQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxPd3h2OG45RG5MYW9ES05PYkRDLXFxWmg1TzFva3g0ZllRamY1TXZfNGM0X3NMMTVaYmk2VHptR2hpUUVoWGJDaDFOVF9hckVTV21WakJFOV9Fa2tsc2NkZUZ1amdCVVBWd195NF9YQjZjV0FoRU9JV2JMZjR6U1lZMkRDZ0t4T1h4eDdTQ082NHNXQlZvWGRSOU5FSUNIb3R2Y0JrSl9OVGtueXBOOW5OaTVBVU9SNmFHcnQ5R3NhdTRJcW1tcXh2VzVOZE5ET3FiQVRwa1FKb3J1UmtnQW9PYzVGSQ?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2385,21 +2385,21 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46142.51332175926</v>
+        <v>46142.31208333333</v>
       </c>
     </row>
     <row r="37">
@@ -2410,27 +2410,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Stau am ersten Mai-Wochenende: ADAC warnt vor langen Wartezeiten - Joyn</t>
+          <t>Yoga in luftiger Höhe: Polizei beendet Video-Dreh auf Ingolstädter Kirchturm - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Traffic jam on the first weekend in May: ADAC warns of long waiting times - Joyn</t>
+          <t>Yoga at dizzy heights: Police end video shoot on Ingolstadt church tower - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:11:56 GMT</t>
+          <t>Thu, 30 Apr 2026 13:10:21 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeVdHLWI0OGkxRkRTOFpaZVNYSXpoTHhNQkROY3Y3aldDa3R6R0lBNDBHcl9FYnpKbWtIUW9iZlNJeXA4Ukw0dVNiRzloa01NS1U5WTBmNFZsU1RSazJSLTRYSEVJLXg3US0wWl9UT05NTGtraXE3eV9pN3h1dy1xdnpKWTJyV1NZY0tsdnJFZE5WY3A5ZlpWRjNUTGR1OGM2cnM1eTRmXzc3enhpaE8xVkZ5NTM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxOMmJiSUNfbFRRTXFjS2VQS0ViVm1IV2JEam95NHB1LTJqMXlFRmlFb0t2aGM4NGxyRXJaRE9nQnNIei1HeW5YOWF2ZXYwVzA5cHhVSG84VGU4UEctRElVX2JQRnZvVHhCb2ZVVXRLbDBjYjk1cmM4Wk42RUdQS0V4Y204VjFwVUhvTFVJbU5uX0g1aGF3MmE1NlVrRVhCWkZfRzI2TzlYR25uSm1HVmJoNlNhclV3blc1ZTJGRDNR?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2454,38 +2454,38 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46142.46662037037</v>
+        <v>46142.54885416666</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Local Town Bicester Kildare</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>("Kildare" OR "M7" OR "Irish Rail" OR "Newbridge") AND (closure OR disruption OR blockade OR evacuation OR accident OR delay OR "road closed" OR protest OR strike) AND -sport AND -GAA AND -horse AND -racing</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Truck accident on the M7, Bluff bound at the N2 interchange. - Arrive Alive</t>
+          <t>Scheinbar religiöse Rituale: Angebliche Wahrsagerin betrügt Frau um mehr als 100.000 Euro - Neue Presse Coburg</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Truck accident on the M7, Bluff bound at the N2 interchange. - Arrive Alive</t>
+          <t>Apparently religious rituals: Alleged fortune teller cheats woman out of more than 100,000 euros - Neue Presse Coburg</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 07:05:28 GMT</t>
+          <t>Thu, 30 Apr 2026 11:35:49 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTm5KcGY1b2U5b0VyLWpkN1hRdVZvbk9VZ1hyMFVQSWFyQVF0NGRKTmJLYU5GOXVSUWRQellxWG9jZXBua29QSEY3RElDS2JnT0oxa3JQYnozZkgzYnFmSmhYQ3BQR1JxVDZ6T1hxemZaYnZrb0ExeWs4aWtTVW9MbFpWcWJQa3FPajJ2QXF6aFR1QTd1OG9aT2h1bXFndktfSTNwTDd0VUdDYW1xMjh3dFZRNVJiQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9gFBVV95cUxPUG43ZGxYWi1Na3RPdnFBWEVpS3lIRTI3NGpNcUxQSF8yZjI3QnpQaGZQWGFvUERyTGhaOTAzTF9lQW42RUJIVnJaR2ozTzNMV2l2bHhldXZrSE1Nc2hCWDZ6WDNsRlJpT0daSlFKc0tuVi1fV1lBXzg2QzFhTVdHREJueF9Vd3lJcS0tdWxjMC1xRzE5dlE4Qm81bVRxcHZmRGNnckpVT2ZaOEsxbEl3T3pNc1NKUmF4Q2NwM29Uc3Jidy1mUFJldTU4NzRxUFlhYnpxZWZudUVha1NLS05KNEExa29kYm5fdXcydERNamZyLTdHOUE?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2495,52 +2495,52 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46142.29546296296</v>
+        <v>46142.48320601852</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>What we know about the Golders Green stabbings - BBC</t>
+          <t>57 Jahre alte Radlerin schwer verletzt bei Frontal-Kollision mit Pkw in Ingolstadt - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>What we know about the Golders Green stabbings - BBC</t>
+          <t>57-year-old cyclist seriously injured in head-on collision with car in Ingolstadt - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:08:57 GMT</t>
+          <t>Thu, 30 Apr 2026 12:19:11 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE80cl9qRWpTaThETlhBQ1N6cTE4QkNXNUFzcHNzMXZHNzRVN3piSEl3bWZoT0ZCanRlcUV4UUZBLVNCdjd6WHNXN3RfU19kUlhCODAtTTRvajZhZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZEFVX3lxTE1oMkRHS0prYlgzZXVLdGxUUFBHdGowWkJkWk53b2d1X1ZiX2dfdGs5Rm1qc0FMOUgzMi1sSXF1bjM5azVfTUcwYlQ3azItaTB5SUVyWEpzbXpyY2hoWVRLcUM0dHQ?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2550,52 +2550,52 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46142.38121527778</v>
+        <v>46142.51332175926</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bodycam footage shows police detaining London stabbing suspect - France 24</t>
+          <t>Stau am ersten Mai-Wochenende: ADAC warnt vor langen Wartezeiten - Joyn</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bodycam footage shows police detaining London stabbing suspect - France 24</t>
+          <t>Traffic jam on the first weekend in May: ADAC warns of long waiting times - Joyn</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:50:44 GMT</t>
+          <t>Thu, 30 Apr 2026 11:11:56 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNaGwtdkV2aVdwTDZvbkVTWkdwVTFfTHVsYWgwSzFua0NkYWw2TklueE5kQm9yMlRSX2lBa0RtRk9jQUxuOHYzbzIyUFMzTzdFcE9KeWo0Q1ZrT01WOTdNVkI2Qlp0MDVJNmppcU4yQnFmU2FmeTJKV3QtNXdiN1ppNHZhckZJZjZaVzAtY1R4M21lN2xSdkxGVm55dHBsZG5yNndjY0dDN2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxPeVdHLWI0OGkxRkRTOFpaZVNYSXpoTHhNQkROY3Y3aldDa3R6R0lBNDBHcl9FYnpKbWtIUW9iZlNJeXA4Ukw0dVNiRzloa01NS1U5WTBmNFZsU1RSazJSLTRYSEVJLXg3US0wWl9UT05NTGtraXE3eV9pN3h1dy1xdnpKWTJyV1NZY0tsdnJFZE5WY3A5ZlpWRjNUTGR1OGM2cnM1eTRmXzc3enhpaE8xVkZ5NTM?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2605,52 +2605,52 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46142.45189814815</v>
+        <v>46142.46662037037</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Local Town Bicester Kildare</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Kildare" OR "M7" OR "Irish Rail" OR "Newbridge") AND (closure OR disruption OR blockade OR evacuation OR accident OR delay OR "road closed" OR protest OR strike) AND -sport AND -GAA AND -horse AND -racing</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Keir Starmer demands ‘swift, agile and visible’ response to London attack - The Guardian</t>
+          <t>Truck accident on the M7, Bluff bound at the N2 interchange. - Arrive Alive</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Keir Starmer demands ‘swift, agile and visible’ response to London attack - The Guardian</t>
+          <t>Truck accident on the M7, Bluff bound at the N2 interchange. - Arrive Alive</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 07:56:00 GMT</t>
+          <t>Thu, 30 Apr 2026 07:05:28 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPMVZnUTU4MFN4WkY4bmpMSEtpS0hQcy01TUVoOFZ3WHFZRU9FdTRFNnZGM1liMFRIeXlkZXRLVG9FY01ORzAtcDdMUTBER3dMclpCYVFYTF9tMUFPNlBGX0lKeUh6ZEo5N29vMURqcGNhSTBBMlVLbDJsN2s5alp3WnlXVzl6TWNRRVRiTnRqV1BNbFd0R0VDa1N5VXNwNVVKTmtoV0hVV19GNjNKOUxPQzhhWVNYb3RZQ25UU2JR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPTm5KcGY1b2U5b0VyLWpkN1hRdVZvbk9VZ1hyMFVQSWFyQVF0NGRKTmJLYU5GOXVSUWRQellxWG9jZXBua29QSEY3RElDS2JnT0oxa3JQYnozZkgzYnFmSmhYQ3BQR1JxVDZ6T1hxemZaYnZrb0ExeWs4aWtTVW9MbFpWcWJQa3FPajJ2QXF6aFR1QTd1OG9aT2h1bXFndktfSTNwTDd0VUdDYW1xMjh3dFZRNVJiQQ?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46142.33055555556</v>
+        <v>46142.29546296296</v>
       </c>
     </row>
     <row r="42">
@@ -2685,27 +2685,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>UK solar growth reaches 10-yr high with 27,000 units in March - Montel News</t>
+          <t>U.K. investigates attacks on Jewish targets for possible links to Iran - The Washington Post</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>UK solar growth reaches 10-yr high with 27,000 units in March - Montel News</t>
+          <t>U.K. investigates attacks on Jewish targets for possible links to Iran - The Washington Post</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 09:45:35 GMT</t>
+          <t>Thu, 30 Apr 2026 13:17:47 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUk5QOXRnTTN3aXhwcG5yOUZmci12SWZNelJBYXFwdTlndHBsRVp2cjNXcHdpLUkzemdFeXRqTWxYWktMY3ZBQmRtTWN2OVhnN05QYk1ZTE1QSUZka0lkQ2Jkb2hQRnFmX1ZrQTZEUWJ5aDlXOUlGVzkyMno2UW9ELUdCQWVieXdyQkhmcy1OWC1vVFNxNE44aXVBQlVON1F6OVpUdDBuWWwzUGwtTkM3c01pcmxCSXUzcGJoQVQ0YnF2R1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQTV9CYTFTMnZ0VGhSNUFCSWh6cmF2OFg5VXdvcmNmQ3VKVktFckZjdTdCVVN0WjZwR3FpRFMtMUpZMEFGSFRmMG0wQXNQTWxEb1ZyV08wbGtPcjRaaEsyTFJJQ19ZQVVXelhPaTBfR1doQTZXQjI3U0F0VnZQUXlsaXFEV0VoTEJjMFpQTWhIbU1hWjI4Y2hmRw?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2729,38 +2729,38 @@
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46142.40665509259</v>
+        <v>46142.55401620371</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
+          <t>What we know about the Golders Green stabbings - BBC</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Procession for Sergio Ramelli in Milan between torches, Roman greetings and insults from the balconies: the video of the "present" - Virgil</t>
+          <t>What we know about the Golders Green stabbings - BBC</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 08:04:00 GMT</t>
+          <t>Thu, 30 Apr 2026 11:49:25 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQS09TOXlYQ2J2d3RYMnc2bVhtTEVmRU8zVEFtQVRBMVM2Y1Rlc0w3QVhjaThzaDhLeER2NGFPQlZxWVl1VDFMTmdhQjBsRENTcmtqUFd1UUxzRC1sNUxkaUFjQVFfNHhNa194WDF2T1dNbm00VnlZU054NUdOT245NUljRE1PanRXTjJWNUNWSU1ZQ0hKLWx6bGt4SUpENlZPdWttWnhKQk4zX2hDMzNLSWY0TjlRTmY4NzRUZk9kZmxwWWN1b19tTzI2Mjk5anhVSEQtV25aWF95SGJiemfSAeMBQVVfeXFMTUVtLU8tTVRJYlg1VHd4X0NpcGM2THRLR3dUVGl3SEFJWTBTSElpNFNoVEhjdjdpOFhhMmQ2X2xtZEFvMWN0elFGeE9BeWtONUpRdkZ2ZmJVY3RJejRsQ09SaTZOREthLU1LMkZ3LVlQXzc0QXQ2cWRoVnk0dFlMVG5WaWZaY0JnVnNmUDhsdG5icUZ0M0VNc0ZYU20tVlpfbGRMN1NpaVU4N29nNUo3QWgySG5iTEktcDZwNXJCZDF2UndPQ3d0aHFUcXZkV2NrSmhMOTg2eDNXTzBPdXlUNEZzN0U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE80cl9qRWpTaThETlhBQ1N6cTE4QkNXNUFzcHNzMXZHNzRVN3piSEl3bWZoT0ZCanRlcUV4UUZBLVNCdjd6WHNXN3RfU19kUlhCODAtTTRvajZhZw?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2770,52 +2770,52 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46142.33611111111</v>
+        <v>46142.49265046296</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
+          <t>'It was horrific': Jewish security volunteers first on scene of Golders Green attack - BBC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
+          <t>'It was horrific': Jewish security volunteers first on scene of Golders Green attack - BBC</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 11:26:44 GMT</t>
+          <t>Thu, 30 Apr 2026 11:20:59 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE9FR1oyZVRJVkZvWTVVWXg5QVg4bmpNaFY2LWZXU1diM3dvczd5MWprX043NzdPUlhRXzNsbE5jLVZmOXV4dDV5SklMem8yclk4VGpIa0FWck5MUQ?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2825,52 +2825,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46142.47689814815</v>
+        <v>46142.4729050926</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Flottilla, presidio davanti alla prefettura di Milano - Radio Lombardia</t>
+          <t>What to Know About the Stabbing Attack Against 2 Jewish Men in London - The New York Times</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Flotilla, garrison in front of the prefecture of Milan - Radio Lombardia</t>
+          <t>What to Know About the Stabbing Attack Against 2 Jewish Men in London - The New York Times</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Thu, 30 Apr 2026 10:18:22 GMT</t>
+          <t>Thu, 30 Apr 2026 13:19:13 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOeVJsdXZta3pROWdpdE95X3NCQUw5NE0xMFFmZ0FucXVlMXR2YzBjcmlLelVfYnk2aHZuSVkyell6eVdDNzlOZnpyNGpubklqeWV4TXhRbUI4Y3hfMkZuZDdTdVRQWHIwcWtSZ25Ha09Hck85bVdhLXFXM2Vzbnk5R2hRaGN2TEMzWTBWd280SGYwTDM1SmJNNUpB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxNdzFseWx4eUJUMjJHcUEtMTVvdXBXU3daVVVMUHNVWjR2TVZvMjNJNzJRQ2IzbFFEN1N2U3lFdzNOa1duYS1aaXUtUlBaenlUZ3dNM1MzaGs4anhfb0taQVBvd1VzNDhFSjQtMGYwZXlfRjZJX2pUbE50RVhwU1E1ZjY1WTVIRU9YelEtTTFsVQ?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,76 +2880,681 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46142.4294212963</v>
+        <v>46142.55501157408</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>High Level City UK Ireland</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bodycam footage shows police detaining London stabbing suspect - France 24</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bodycam footage shows police detaining London stabbing suspect - France 24</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:50:44 GMT</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxNaGwtdkV2aVdwTDZvbkVTWkdwVTFfTHVsYWgwSzFua0NkYWw2TklueE5kQm9yMlRSX2lBa0RtRk9jQUxuOHYzbzIyUFMzTzdFcE9KeWo0Q1ZrT01WOTdNVkI2Qlp0MDVJNmppcU4yQnFmU2FmeTJKV3QtNXdiN1ppNHZhckZJZjZaVzAtY1R4M21lN2xSdkxGVm55dHBsZG5yNndjY0dDN2U?oc=5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K46" s="1" t="n">
+        <v>46142.45189814815</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>High Level City UK Ireland</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Keir Starmer demands ‘swift, agile and visible’ response to London attack - The Guardian</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Keir Starmer demands ‘swift, agile and visible’ response to London attack - The Guardian</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 07:56:00 GMT</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPMVZnUTU4MFN4WkY4bmpMSEtpS0hQcy01TUVoOFZ3WHFZRU9FdTRFNnZGM1liMFRIeXlkZXRLVG9FY01ORzAtcDdMUTBER3dMclpCYVFYTF9tMUFPNlBGX0lKeUh6ZEo5N29vMURqcGNhSTBBMlVLbDJsN2s5alp3WnlXVzl6TWNRRVRiTnRqV1BNbFd0R0VDa1N5VXNwNVVKTmtoV0hVV19GNjNKOUxPQzhhWVNYb3RZQ25UU2JR?oc=5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K47" s="1" t="n">
+        <v>46142.33055555556</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>High Level City UK Ireland</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>UK solar growth reaches 10-yr high with 27,000 units in March - Montel News</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>UK solar growth reaches 10-yr high with 27,000 units in March - Montel News</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 09:45:35 GMT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUk5QOXRnTTN3aXhwcG5yOUZmci12SWZNelJBYXFwdTlndHBsRVp2cjNXcHdpLUkzemdFeXRqTWxYWktMY3ZBQmRtTWN2OVhnN05QYk1ZTE1QSUZka0lkQ2Jkb2hQRnFmX1ZrQTZEUWJ5aDlXOUlGVzkyMno2UW9ELUdCQWVieXdyQkhmcy1OWC1vVFNxNE44aXVBQlVON1F6OVpUdDBuWWwzUGwtTkM3c01pcmxCSXUzcGJoQVQ0YnF2R1U?oc=5</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K48" s="1" t="n">
+        <v>46142.40665509259</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Flottilla, presidio davanti alla prefettura di Milano - Radio Lombardia</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Flotilla, garrison in front of the prefecture of Milan - Radio Lombardia</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 10:18:22 GMT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOeVJsdXZta3pROWdpdE95X3NCQUw5NE0xMFFmZ0FucXVlMXR2YzBjcmlLelVfYnk2aHZuSVkyell6eVdDNzlOZnpyNGpubklqeWV4TXhRbUI4Y3hfMkZuZDdTdVRQWHIwcWtSZ25Ha09Hck85bVdhLXFXM2Vzbnk5R2hRaGN2TEMzWTBWd280SGYwTDM1SmJNNUpB?oc=5</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K49" s="1" t="n">
+        <v>46142.4294212963</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Corteo per Sergio Ramelli a Milano tra fiaccole, saluti romani e insulti dai balconi: il video del "presente" - Virgilio</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Procession for Sergio Ramelli in Milan between torches, Roman greetings and insults from the balconies: the video of the "present" - Virgil</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 08:04:00 GMT</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxQS09TOXlYQ2J2d3RYMnc2bVhtTEVmRU8zVEFtQVRBMVM2Y1Rlc0w3QVhjaThzaDhLeER2NGFPQlZxWVl1VDFMTmdhQjBsRENTcmtqUFd1UUxzRC1sNUxkaUFjQVFfNHhNa194WDF2T1dNbm00VnlZU054NUdOT245NUljRE1PanRXTjJWNUNWSU1ZQ0hKLWx6bGt4SUpENlZPdWttWnhKQk4zX2hDMzNLSWY0TjlRTmY4NzRUZk9kZmxwWWN1b19tTzI2Mjk5anhVSEQtV25aWF95SGJiemfSAeMBQVVfeXFMTUVtLU8tTVRJYlg1VHd4X0NpcGM2THRLR3dUVGl3SEFJWTBTSElpNFNoVEhjdjdpOFhhMmQ2X2xtZEFvMWN0elFGeE9BeWtONUpRdkZ2ZmJVY3RJejRsQ09SaTZOREthLU1LMkZ3LVlQXzc0QXQ2cWRoVnk0dFlMVG5WaWZaY0JnVnNmUDhsdG5icUZ0M0VNc0ZYU20tVlpfbGRMN1NpaVU4N29nNUo3QWgySG5iTEktcDZwNXJCZDF2UndPQ3d0aHFUcXZkV2NrSmhMOTg2eDNXTzBPdXlUNEZzN0U?oc=5</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K50" s="1" t="n">
+        <v>46142.33611111111</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:26:44 GMT</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K51" s="1" t="n">
+        <v>46142.47689814815</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>“L’ADIGE.IT” * ATTUALITÀ: «A MILANO CONCLUSO IL CORTEO PER RAMELLI CON SALUTI ROMANI» - agenziagiornalisticaopinione.it</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>“L’ADIGE.IT” * NEWS: «THE PROCESSION FOR RAMELLI CONCLUDED IN MILAN WITH ROMAN GREETINGS» - agenziagiornalisticaeconomia.it</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 07:03:32 GMT</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxPU0w4SHZBbm5uanQ0MW5wZ04xZzNVOTQ3RWh1b1NqRFNjeGo3dWFPZ2dXWV9ZZWVPWW9FOG8wUW52cUtESGZWeER3Q3dwR2JhV3lTX3FVOWhYdnQtdlBTUVBXMVB4Z1ZQUlBsOVhUeG1GS3hIb1cza1JWRTd5QmlGWVpzUjJuaVJiYmVFTGoySk9lV05nWE9VRC1nN25GMW55cDZiV2paRzVtMXhHdkdxUzU1YlB1ek4xVE9lM2V0UnRIQWVfalN6RzBWV2IyQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K52" s="1" t="n">
+        <v>46142.29412037037</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>Local Town Fidenza Italian</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B53" t="inlineStr">
         <is>
           <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>Blocco dell’autostrada al Brennero sabato 30 maggio, il “no” di Conftrasporto - Vita Trentina</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>Blocking of the Brenner motorway on Saturday 30 May, Conftrasporto's "no" - Vita Trentina</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 09:40:46 GMT</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxQNTVmdG9LQW85ZmU3elpmTHBSbS1EOTdUb29MNTRhdzk5bl9PcG9VWGJSUnRWWVBqUTV2bFJXWVpQOTBsb0o3VUVKLVVCaV9MaUJ0RTRXQlF0eC1pbC04bDBKS1FkR0h4NzVPOXpHVHFEWmNJLU52SWg3RHlRZFVFaFNhTlJtUklLVk4tcmEyRVBZWDZJM0tpMVMxOWZfbi0yNDk5dk95dDhZMVE1RE9Nc0MyWQ?oc=5</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
         <is>
           <t>it</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>IT:it</t>
         </is>
       </c>
-      <c r="K46" s="1" t="n">
+      <c r="K53" s="1" t="n">
         <v>46142.40331018518</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Local Town Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Siena, incidente sull’A1: morto il ragazzo di 25 anni. Sempre grave la fidanzata – Chi è la vittima - Il Tirreno</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Siena, accident on the A1: the 25-year-old boy dies. The girlfriend is always serious - Who is the victim - Il Tirreno</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 13:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOWTF6UnB5MGFtYjhDSDZObUdVZFVIa2RmajZBT1VBQnlWQkJHcFBUMTRUZTF3SWVNdkVBWG9oeU5icEhDZDdwYkliSlFmelA5N1ltYnVxNElXZWN5a1NqYW44U2E1emlRQTZLMm9NRl9XRm9QclVKaG9FU1dJRzlQQ19tblR5REVwSmU0c2U4R0ppMG0wSU40MzZtX3c0QU05RkYwVFBwcTZqdEtfUjVlSDFDYjhvMXM5YUFXOVYySVFIOTM0Q3FCWllYeGp6NmZZX0hTQVZ1X1p6UVI3TmRrT0F5dGFMWW8?oc=5</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K54" s="1" t="n">
+        <v>46142.55833333333</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Local Town Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Pietro muore nell'incidente a soli 25 anni - Polesine24</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Pietro dies in the accident at just 25 years old - Polesine24</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:24:00 GMT</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxNeEd6dTEzSkhhcVFPLWxzX1EwVHFwejNoUlkyUm1ZLU9rU1ZaT1J1ZUVuNkJpQlE3NjBSYWRRU1d0ZjVndkE2Q2phc2NRb0o2Yk5GZjhMaS1wcTJFR1hCaHI2VlExdnR1Um80OXRTV081VkstSWNneWwzUjcxNFpYU2tFUkd3cXpWWlE3aWNmdHl5RFZKcUM2aEstZ0NUUHdwOEE?oc=5</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K55" s="1" t="n">
+        <v>46142.475</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Local Town Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Incidenti camion con perdita di carico: quali responsabilità dopo il caso A1 - SICURAUTO.it</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Truck accidents with loss of load: what responsibilities after the A1 case - SICURAUTO.it</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 11:45:00 GMT</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxQZlJPdFBrYXk4SkZGUXUwTWxuZ2tzcWlfdXFVeHJSVVRERWRfZDAyVnZjbmNlcG5uSk52cHp3YURUS3Y4OWZwSks2RUw5NmhxUU1aeDQxZG9lYTBhMlV2WVhmRFBYVEdXVm5LV2ZzMElEM0UxaW5RMmV0NUVWZ1MtaUc1Q0gtT0JvRUlUajJSdlphdlQzTEdSTnFtcVRYVnNSaFdzSzQyRlNkb1VnZzA2YnVOV3NhLUY0cEREazc1akl6QUx5?oc=5</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K56" s="1" t="n">
+        <v>46142.48958333334</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Local Town Fidenza Italian</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Pietro Bellato muore a 25 anni due giorni dopo l'incidente: la sua auto è stata travolta dalle bobine cadute da un camion. Grave la... - Il Mattino</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Pietro Bellato dies at the age of 25 two days after the accident: his car was hit by coils that fell from a truck. Serious the... - The Morning</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Thu, 30 Apr 2026 09:55:41 GMT</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOMkFvZy03cWtYTE1NX21ENXc2NGp3ckphazhzY01mczVnY3laSHh1SE5VRURmSjBoaW5kWW11RVVoV1J5VHVBZm56dGxMdVBHaVhBd0Jzbk9aS1NhZ1hmLWhfeXB2M1JzeHozMGhadHh1MHcwcjJES3Itb0JIVUsySHdOSFo1YmVPX19adUYydk9sNVMtUTk5aXN6aHlOYXJtc2Nld1d6Yk9rdjlfU2NpMGFJeTE1SmZ1ZGJjZUdQaGtULXZlN2fSAcYBQVVfeXFMTjJBb2ctN3FrWExNTV9tRDV3NjRqd3JKYWs4c2NNZnM1Z2N5Wkh4dUhOVUVEZkowaGluZFltdUVVaFdSeVR1QWZuenRsTHVQR2lYQXdCc25PWktTYWdYZi1oX3lwdjNSc3h6MzBoWnR4dTB3MHIyREtyLW9CSFVLMkh3TkhaNWJlT19fWnVGMnZPbDVTLVE5OWlzemh5TmFybXNjZXdXemJPa3Y5X1NjaTBhSXkxNUpmdWRiY2VHUGhrVC12ZTdn?oc=5</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K57" s="1" t="n">
+        <v>46142.41366898148</v>
       </c>
     </row>
   </sheetData>
